--- a/Teensy-pin-mapping-Diff-VM-revB.xlsx
+++ b/Teensy-pin-mapping-Diff-VM-revB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\randa\Documents\Arduino\OpenSourceDiffVM-RevB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{214A3960-4907-4F13-A8C7-528C437DFBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81256A20-DAB6-4C7B-91BC-CBF2B4050A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15495" windowHeight="14340" xr2:uid="{B74B6C3A-238E-44FF-8610-E3FD92680C64}"/>
   </bookViews>
@@ -137,12 +137,6 @@
     <t>RESET_ADC - 40</t>
   </si>
   <si>
-    <t>HV-A0</t>
-  </si>
-  <si>
-    <t>HV-A1</t>
-  </si>
-  <si>
     <t>MUX-A0</t>
   </si>
   <si>
@@ -153,6 +147,12 @@
   </si>
   <si>
     <t>ADC pins + HV/MUX</t>
+  </si>
+  <si>
+    <t>HV-A0 - 23</t>
+  </si>
+  <si>
+    <t>HV-A1 - 22</t>
   </si>
 </sst>
 </file>
@@ -221,10 +221,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -562,7 +558,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>24</v>
@@ -590,7 +586,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -604,7 +600,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -897,7 +893,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <v>35</v>
@@ -911,7 +907,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1">
         <v>34</v>
@@ -925,7 +921,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1">
         <v>33</v>
@@ -940,15 +936,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005851A70D5B2200428006708B132449A6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77b02b980851081397f76f7379f27343">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="660eeea4-7c07-4521-ad03-700aa6a51e84" xmlns:ns4="a7727a5c-bafa-4d79-9be4-ea5186874d9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0d1a87144903906c6d178c75244bb8b9" ns3:_="" ns4:_="">
     <xsd:import namespace="660eeea4-7c07-4521-ad03-700aa6a51e84"/>
@@ -1175,6 +1162,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1184,14 +1180,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86074211-462B-4D14-8AAF-B3F6E765EA96}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99DC4A08-63B0-4CBF-979F-AEFC636A3DD7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1206,6 +1194,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86074211-462B-4D14-8AAF-B3F6E765EA96}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
